--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0033.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0033.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Bổ Sung Dice I</t>
+          <t>Xúc Xắc Phụ I</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Bổ Sung Move</t>
+          <t>Đòn Bổ Sung</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Bổ Sung Dice II</t>
+          <t>Xúc Xắc Phụ II</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Speed Boost II</t>
+          <t>Tăng Tốc II</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Safety Net</t>
+          <t>Lưới An Toàn</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Double Rewards</t>
+          <t>Phần Thưởng Nhân Đôi</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Bổ Sung Dice I</t>
+          <t>Xúc Xắc Phụ I</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Speed Boost I</t>
+          <t>Tăng Tốc I</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Speed Boost I</t>
+          <t>Tăng Tốc I</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Thrice Rebound</t>
+          <t>Phản Xạ Ba Lần</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Thrice Rebound</t>
+          <t>Phản Xạ Ba Lần</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Double Dare</t>
+          <t>Thách thức kép</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Double Dare</t>
+          <t>Thách thức kép</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Bổ Sung Move</t>
+          <t>Đòn Bổ Sung</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Đạt 100 điểm Hoạt động Sổ tay Hướng dẫn</t>
+          <t>Thu thập 100 Điểm Hoạt Động Sổ Tay Hướng Dẫn</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Đang Tiến Hành</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Đang Trong Round Thi Đấu</t>
+          <t>Đang Trong Vòng Thi Đấu</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Round Locked</t>
+          <t>Vòng bị khóa.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Insufficient Dice</t>
+          <t>Xúc xắc không đủ</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Round đấu này chưa được mở khóa</t>
+          <t>Vòng đấu này chưa được mở khóa</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Nhân đôi</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Đã nhận tất cả phần thưởng</t>
+          <t>Đã nhận tất cả phần thưởng.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Training Tasks</t>
+          <t>Nhiệm vụ Huấn luyện</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Daily Tasks</t>
+          <t>Nhiệm Vụ Hằng Ngày</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Weekly Tasks</t>
+          <t>Nhiệm Vụ Hàng Tuần</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Version Tasks</t>
+          <t>Nhiệm Vụ Phiên Bản</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Double Drop Chances Hôm nay:</t>
+          <t>Cơ Hội Nhân Đôi Hôm Nay:</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Night Special: Silly Jelly</t>
+          <t>Đặc Biệt Đêm: Thạch Ngốc Nghếch</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Night Special: Prickly Feast</t>
+          <t>Đặc Biệt Đêm: Bữa Tiệc Gai Góc</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Claimable</t>
+          <t>Có thể nhận</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Indifferent</t>
+          <t>Thờ ơ</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Pat pat</t>
+          <t>Vỗ vỗ</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Unhappy</t>
+          <t>Không Vui</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Leaving</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Take note</t>
+          <t>Ghi chú lại</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Puzzled</t>
+          <t>Bối rối</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Stunned</t>
+          <t>Bị Choáng</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Hello</t>
+          <t>Xin chào</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Envy</t>
+          <t>Ghen tị</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Distressed</t>
+          <t>Đau Khổ</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Giận dữ</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Like</t>
+          <t>Giống như</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>HAHA</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Daydreaming</t>
+          <t>Mơ Giữa Ban Ngày</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Listening</t>
+          <t>Đang nghe</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Kéo away</t>
+          <t>Kéo ra xa</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Thu thập bạn</t>
+          <t>Thu thập cậu</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Drink</t>
+          <t>Đồ Uống</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Leave it to me</t>
+          <t>Để đó cho tôi</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Amazing</t>
+          <t>Tuyệt vời</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Escape</t>
+          <t>Thoát Hiểm</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Okay</t>
+          <t>Được rồi.</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Don't provoke me</t>
+          <t>Đừng khiêu khích tao.</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Hạnh phúc</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Thinking</t>
+          <t>Suy nghĩ...</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>What did you say</t>
+          <t>Cậu vừa nói gì</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Chaotic</t>
+          <t>Hỗn Loạn</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Give you heart</t>
+          <t>Trao anh trái tim này</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Go you</t>
+          <t>Con đi đi.</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Send flowers</t>
+          <t>Gửi hoa</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Cool</t>
+          <t>Ngầu</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Goodbye</t>
+          <t>Tạm biệt.</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Good night</t>
+          <t>Chúc ngủ ngon.</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Arrived</t>
+          <t>Đã đến nơi</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>Giận dữ</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Xem thử</t>
+          <t>Xem thử đi</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>What</t>
+          <t>Gì...</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Like</t>
+          <t>Giống như</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Tired</t>
+          <t>Mệt mỏi</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>What to eat</t>
+          <t>Ăn gì bây giờ nhỉ?</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Đòn đánh</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Speechless</t>
+          <t>Cạn Lời</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Drink tea</t>
+          <t>Uống trà đi</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Helpless</t>
+          <t>Bất lực</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Shy</t>
+          <t>Ngại ngùng</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>In Peace</t>
+          <t>Trong Bình Yên</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Nod</t>
+          <t>Gật đầu</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Challenge: Fish for Love</t>
+          <t>Thử Thách: Câu Cá Tình Yêu</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Night Special: Phantom Trap</t>
+          <t>Đặc Biệt Đêm: Bẫy Ảo Giác</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Special Night: Dây Cương Bên Trái Của Thần Mặt Trời</t>
+          <t>Đặc Biệt Đêm: Dây Cương Bên Trái Của Thần Mặt Trời</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Special Night: Dây Cương Bên Right Của Thần Mặt Trời</t>
+          <t>Đặc Biệt Đêm: Dây Cương Bên Phải Của Thần Mặt Trời</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Challenge: Mimicry</t>
+          <t>Thử Thách: Bắt Chước</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Challenge: Airweaver</t>
+          <t>Thách đấu: Airweaver</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Challenge: True Delicacy</t>
+          <t>Thử Thách: Món Ngon Chính Hiệu</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Challenge Night: Night Sáng Rực</t>
+          <t>Thử Thách Đêm: Luminous Night</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Challenge Night: Bạch Tuộc và Sao Biển</t>
+          <t>Thử Thách Đêm: Bạch Tuộc và Sao Biển</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Challenge: Gaze from the Dead</t>
+          <t>Thử Thách: Ánh Mắt Từ Cõi Chết</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Challenge: Rainbow Duet</t>
+          <t>Thử Thách: Song Tấu Cầu Vồng</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Challenge Night: Cá Chạy Trốn</t>
+          <t>Thử Thách Đêm: Cá Chạy Trốn</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Challenge: Red Horned Mobile Suit</t>
+          <t>Thử Thách: Bộ Giáp Di Động Sừng Đỏ</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Challenge: The Hermit of Legends</t>
+          <t>Thử Thách: Ẩn Sĩ Huyền Thoại</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Challenge: End Săn Đuổi</t>
+          <t>Thử Thách: Kết Thúc Săn Đuổi</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Không Bell Please</t>
+          <t>Xin đừng rung chuông</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Night Fishing: Nâng Cốc Vì Salp</t>
+          <t>Câu Cá Đêm: Nâng Cốc Vì Salp</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Ahab's Request: Meet the Phantom</t>
+          <t>Yêu cầu của Ahab: Gặp Gỡ Hồn Ma</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>The Sun Chaser</t>
+          <t>Kẻ Đuổi Theo Mặt Trời</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Night Fishing: Long Fishing Season</t>
+          <t>Câu Cá Đêm: Mùa Câu Kéo Dài</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Til Death Do Us Part</t>
+          <t>Đến Khi Chết Cách Xa</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Night Fishing: Jelly Party</t>
+          <t>Câu Cá Đêm: Bữa Tiệc Sứa</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Catch Salp</t>
+          <t>Bắt Sứa Salp</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Catch Pokey Moray</t>
+          <t>Bắt Cá Moray Gai Nhọn</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Catch Dead Man's Eye</t>
+          <t>Bắt Mắt Người Chết</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Catch Astrite Crab</t>
+          <t>Bắt Astrite Crab</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Catch Rainbow Dolphinfish</t>
+          <t>Bắt Cá Chuồn Cầu Vồng</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Catch Aureo Shark</t>
+          <t>Bắt Aureo Shark</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Catch Draco Cobia</t>
+          <t>Bắt Draco Cobia</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Catch Octopus Clam Mutant</t>
+          <t>Bắt Biến Thể Sò Bạch Tuộc</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Catch Til the Fin-ish Mutant</t>
+          <t>Bắt Biến Thể Til the Fin-ish</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Catch Giant Gulper Mutant</t>
+          <t>Bắt Cá Hố Khổng Lồ Đột Biến</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Catch Gooberstar Mutant</t>
+          <t>Bắt Sao Goober Đột Biến</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Catch Stygian Phantom Mutant</t>
+          <t>Bắt Biến Thể Hồn Ma Stygian</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Catch Bubble Snail Mutant</t>
+          <t>Bắt Ốc Bong Bóng Đột Biến</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Catch Astrite Crab Mutant</t>
+          <t>Bắt Astrite Crab Đột Biến</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Catch Reinfish Mutant</t>
+          <t>Bắt Cá Reinfish Đột Biến</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Here I Am</t>
+          <t>Ta Đến Đây</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Sob</t>
+          <t>Hức...</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Let's Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Greet</t>
+          <t>Xin chào.</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Rich</t>
+          <t>Giàu có</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Wow</t>
+          <t>Ồ!</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Cảm ơn</t>
+          <t>Cảm ơn.</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Sleepy</t>
+          <t>Buồn ngủ</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Clock Out</t>
+          <t>Hết ca</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Don't Rush</t>
+          <t>Đừng Có Vội</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>What</t>
+          <t>Gì...</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Good Job</t>
+          <t>Làm Tốt Lắm</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Poof</t>
+          <t>Phù!</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Relax</t>
+          <t>Thư giãn nào</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Punch</t>
+          <t>Đấm</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Okiee</t>
+          <t>Oki</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Buồn</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Pat</t>
+          <t>Vỗ</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>Bất ngờ</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Huh</t>
+          <t>Hử?</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Get</t>
+          <t>Lấy</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Lion Dance</t>
+          <t>Múa Sư Tử</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Hi</t>
+          <t>Chào</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>See Through</t>
+          <t>Nhìn Thấu</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Nhìn chằm chằm</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Electric Shock</t>
+          <t>Điện Giật</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Flute</t>
+          <t>Sáo</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Confused</t>
+          <t>Bối Rối</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Excited</t>
+          <t>Hào hứng</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>Bình tĩnh</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Carefree</t>
+          <t>Thảnh thơi</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Hello</t>
+          <t>Xin chào</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Rút</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Wink</t>
+          <t>Nháy Mắt</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Shocked</t>
+          <t>Bị sốc điện</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Light-Bulb</t>
+          <t>Bóng đèn</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Hug</t>
+          <t>Ôm</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Please</t>
+          <t>Làm ơn</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Cry</t>
+          <t>Khóc đi</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Upset</t>
+          <t>Bực Mình</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Đòn đánh</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Hmph</t>
+          <t>Hừ!</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Food Please</t>
+          <t>Cho tôi đồ ăn với</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Cold Sweat</t>
+          <t>Mồ Hôi Lạnh</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Chill</t>
+          <t>Bình tĩnh</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Hooray</t>
+          <t>Hoan hô!</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Curious</t>
+          <t>Tò Mò</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Splat</t>
+          <t>Bẹp</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Heart</t>
+          <t>Trái tim</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Polish Shoes</t>
+          <t>Đánh Giày</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Show Time</t>
+          <t>Hiển thị Thời Gian</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Anyone Here</t>
+          <t>Có ai ở đây không?</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Smile</t>
+          <t>Nụ cười</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Private chat</t>
+          <t>Trò Chuyện Riêng</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Current Đội</t>
+          <t>Đội Hình Hiện Tại</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Thử thách Permanent</t>
+          <t>Thử thách Vĩnh viễn</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Proceed</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Tất cả Quests Completed</t>
+          <t>Đã Hoàn Thành Tất Cả Nhiệm Vụ</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Chưa bắt đầu</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Vật phẩm Obtained</t>
+          <t>Đã nhận được vật phẩm</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Returned Item</t>
+          <t>Vật phẩm đã trả lại</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Proficiency</t>
+          <t>Thành thạo</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Cooking completed</t>
+          <t>Nấu xong rồi</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Cooking completed</t>
+          <t>Nấu xong rồi</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Crafting Completed</t>
+          <t>Hoàn thành chế tác</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Nghiên cứu EXP</t>
+          <t>Kinh nghiệm nghiên cứu</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Nghiên cứu Completed</t>
+          <t>Hoàn thành nghiên cứu</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Cooking failed</t>
+          <t>Nấu hỏng mất rồi</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Delivery Completed</t>
+          <t>Đã giao hàng xong</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Apprentice</t>
+          <t>Học Trò</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Assistant Chef</t>
+          <t>Phụ bếp</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Sous Chef</t>
+          <t>Phụ Bếp</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Head Chef</t>
+          <t>Bếp trưởng</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Top Chef</t>
+          <t>Đầu Bếp Xuất Sắc Nhất</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Waveplate Consumption</t>
+          <t>Tiêu Hao Tấm Điều Chỉnh Sóng</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Random Nation</t>
+          <t>Quốc gia Ngẫu Nhiên</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Flying Yarn</t>
+          <t>Sợi Chỉ Bay</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Where the Pincers Lead</t>
+          <t>Nơi Những Càng Kìm Dẫn Lối</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Gulp of Blob</t>
+          <t>Ực... Blob...</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Feather Bloom</t>
+          <t>Lông Vũ Nở Rộ</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Feather Bloom</t>
+          <t>Lông Vũ Nở Rộ</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Rainbow Duet</t>
+          <t>Bản Song Tấu Cầu Vồng</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Night Fishing: Nothing Gained</t>
+          <t>Câu Cá Đêm: Chẳng Được Gì Cả</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Predator and Prey</t>
+          <t>Thợ Săn và Con Mồi</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Night Fishing: Holy Crab</t>
+          <t>Câu Cá Đêm: Cua Thánh</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Crimson Comet</t>
+          <t>Sao Chổi Đỏ Thẫm</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Night Fishing: Ký Ức Về Thần Biển</t>
+          <t>Câu Cá Đêm: Ký Ức Về Thần Biển</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Night Fishing: Astrite Từ Thủy Thần</t>
+          <t>Câu Cá Đêm: Astrite from the Sea God</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Beohr Waters</t>
+          <t>Vực Nước Beohr</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Capitoline Hill City</t>
+          <t>Đồi Capitoline Thành Phố</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Colosseum Olymdos</t>
+          <t>Đấu Trường Olymdos</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Capitoline Foothills</t>
+          <t>Chân đồi Capitoline</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Titanbone Expanse</t>
+          <t>Vùng Đất Xương Titan</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Border Mountains</t>
+          <t>Núi Biên Giới</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Mournfell Canyon</t>
+          <t>Hẻm Núi Mournfell</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Ashen Dragon's Crypt</t>
+          <t>Hầm Mộ Rồng Tro Tàn</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Remnant Cubes</t>
+          <t>Khối Tàn Tích</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Realm of Melodies</t>
+          <t>Tổ Tacet Giai Điệu</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Fiery Arpeggio of Summer Reunion</t>
+          <t>Khúc Giao Hưởng Mùa Hè Rực Lửa</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Lightly We Toss the Crown</t>
+          <t>Chúng ta nhẹ nhàng ném vương miện</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Calamity</t>
+          <t>Bản Hologram Chiến Thuật: Đại Họa</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Phantom Pain</t>
+          <t>Hologram Chiến Thuật: Nỗi Đau Ảo Ảnh</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Synchronization</t>
+          <t>Hologram Chiến Thuật: Đồng Bộ Hóa</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Unknown Ability: Unbound</t>
+          <t>Kỹ năng Không xác định: Unbound</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Unknown Ability: Halo</t>
+          <t>Kỹ năng Không xác định: Halo</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Unknown Ability: Swiftbreak</t>
+          <t>Kỹ năng Không xác định: Swiftbreak</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Unknown Ability: Smash</t>
+          <t>Kỹ năng Không xác định: Smash</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Unknown Ability: Mirror Blessing</t>
+          <t>Kỹ năng Không xác định: Mirror Blessing</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Vibration</t>
+          <t>Rung động</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Valor</t>
+          <t>Dũng Khí</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Wisdom</t>
+          <t>Trí Tuệ</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Counterattack</t>
+          <t>Phản công</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Swiftness</t>
+          <t>Tốc Độ</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>Đà Tiến</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Efficiency</t>
+          <t>Hiệu Suất</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Robustness</t>
+          <t>Sức Bền</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Resurgence</t>
+          <t>Sự Trỗi Dậy</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>DNS Resolution</t>
+          <t>Phân Giải DNS</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Web Access Test</t>
+          <t>Kiểm Tra Truy Cập Mạng</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Testing…</t>
+          <t>Đang kiểm tra…</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Ping Test</t>
+          <t>Kiểm Tra Ping</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Ping Results:</t>
+          <t>Kết Quả Ping:</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Proxy Test</t>
+          <t>Bài Kiểm Tra Ủy Quyền</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Chọn máy chủ</t>
+          <t>Chọn Máy Chủ</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Bắt đầu thử nghiệm</t>
+          <t>Bắt Đầu Kiểm Tra</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Network Test</t>
+          <t>Kiểm Tra Mạng</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Trace ID:</t>
+          <t>ID Theo Dõi:</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>UDP Connectivity Test</t>
+          <t>Kiểm tra kết nối UDP</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Route Detection</t>
+          <t>Phát Hiện Lộ Trình</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Acropolis Documentarian I</t>
+          <t>Nhà Biên Ký Acropolis I</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Acropolis Documentarian II</t>
+          <t>Nhà Biên Ký Acropolis II</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Acropolis Documentarian III</t>
+          <t>Nhà Biên Ký Acropolis III</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Acropolis Documentarian IV</t>
+          <t>Nhà Biên Ký Acropolis IV</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Acropolis Documentarian V</t>
+          <t>Nhà Biên Ký Acropolis V</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Acropolis Documentarian VI</t>
+          <t>Nhà Biên Ký Acropolis VI</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Du ký Ký ức</t>
+          <t>Biên Niên Ký Ức</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Memory Travelogue I</t>
+          <t>Hồi Ký Ký Ức I</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Memory Travelogue II</t>
+          <t>Hồi Ký Ký Ức II</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Memory Travelogue III</t>
+          <t>Hồi Ký Ký Ức III</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Memory Travelogue IV</t>
+          <t>Hồi Ký Ký Ức IV</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Memory Travelogue V</t>
+          <t>Hồi Ký Ký Ức V</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Memory Travelogue VI</t>
+          <t>Hồi Ký Ký Ức VI</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Memory Travelogue VII</t>
+          <t>Hồi Ký Ký Ức VII</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Memory Travelogue VIII</t>
+          <t>Hồi Ký Ký Ức VIII</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Memory Travelogue IX</t>
+          <t>Hồi Ký Ký Ức IX</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Memory Travelogue X</t>
+          <t>Hồi Ký Ký Ức X</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Memory Travelogue XI</t>
+          <t>Hồi Ký Ký Ức XI</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Memory Travelogue XII</t>
+          <t>Hồi Ký Ký Ức XII</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Memory Travelogue XIII</t>
+          <t>Hồi Ký Du Hành XIII</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Uncovering Past Heroes I</t>
+          <t>Khám Phá Anh Hùng Xưa I</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Uncovering Past Heroes II</t>
+          <t>Những Anh Hùng Xưa II</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Uncovering Past Heroes III</t>
+          <t>Những Anh Hùng Xưa III</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Uncovering Past Heroes IV</t>
+          <t>Những Anh Hùng Xưa IV</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Uncovering Past Heroes V</t>
+          <t>Những Anh Hùng Xưa V</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Uncovering Past Heroes VI</t>
+          <t>Những Anh Hùng Xưa VI</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Idle Animation: II</t>
+          <t>Động tác chờ: II</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Idle Animation: III</t>
+          <t>Động tác chờ: III</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Chương II Act IV</t>
+          <t>Chương II Hồi IV</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Shadow Glory</t>
+          <t>Bóng Tối Vinh Quang</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Chương II Act V</t>
+          <t>Chương II Hồi V</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Reprise Rewards</t>
+          <t>Phần Thưởng Tái Ngộ</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Reprise Tasks</t>
+          <t>Nhiệm Vụ Tái Ngộ</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Daily Task</t>
+          <t>Nhiệm Vụ Ngày</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Recurring Task</t>
+          <t>Nhiệm Vụ Lặp Lại</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Phần thưởng tiến trình</t>
+          <t>Phần thưởng Tiến triển</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Tăng Gấp Đôi Rơi Vật Phẩm</t>
+          <t>Nhân Đôi Rơi Vật Phẩm</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Head to Lahai-Roi</t>
+          <t>Đến Lahai-Roi đi</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Log in to the game</t>
+          <t>Đăng nhập vào game</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Đạt 100 điểm Hoạt động Sổ tay Hướng dẫn</t>
+          <t>Thu thập 100 Điểm Hoạt Động Sổ Tay Hướng Dẫn</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Hoàn thành 1 Chương Nhiệm Vụ Chính hoặc 1 Companion Story.</t>
+          <t>Hoàn thành 1 Chương Nhiệm Vụ Chính hoặc 1 Câu Chuyện Đồng Hành.</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Thu thập 4.000 Points Ảo Ảnh trong "Fantasies of the Thousand Gateways" hiện tại</t>
+          <t>Thu thập 4.000 Điểm Ảo Ảnh trong "Ảo Ảnh Ngàn Cánh Cổng" hiện tại</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Thu thập 230 Bản Ghi Nguy Hiểm trong Tower of Adversity</t>
+          <t>Thu thập 230 Bản Ghi Nguy Hiểm trong Tháp Nghịch Cảnh</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Hoàn thành 1 Chương Nhiệm Vụ Chính hoặc 1 Companion Story (Nhận thưởng tối đa 2 lần)</t>
+          <t>Hoàn thành 1 Chương Nhiệm Vụ Chính hoặc 1 Câu Chuyện Đồng Hành (Nhận thưởng tối đa 2 lần)</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Log in to the game</t>
+          <t>Đăng nhập vào game</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Đạt 100 điểm Hoạt động Sổ tay Hướng dẫn</t>
+          <t>Thu thập 100 Điểm Hoạt Động Sổ Tay Hướng Dẫn</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Hoàn thành 1 Chương Nhiệm Vụ Chính hoặc 1 Companion Story (Nhận thưởng tối đa 4 lần)</t>
+          <t>Hoàn thành 1 Chương Nhiệm Vụ Chính hoặc 1 Câu Chuyện Đồng Hành (Nhận thưởng tối đa 4 lần)</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Tune Echoes 10 times</t>
+          <t>Vang Tần 10 lần</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Tune Echoes 25 times</t>
+          <t>Điều Chỉnh Tần Số 25 lần.</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>ATK Bonus</t>
+          <t>Tăng ATK</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Khuếch đại DMG</t>
+          <t>Khuếch Đại Sát Thương</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>DMG Reduction</t>
+          <t>Giảm Sát Thương</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Movement Speed Bonus</t>
+          <t>Thưởng Tốc Độ Di Chuyển</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Max STA &amp; Recovery</t>
+          <t>STA và phục hồi đã đạt tối đa</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Movement Speed +16%</t>
+          <t>Tốc Độ Di Chuyển +16%</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Pickup Range +50%</t>
+          <t>Tầm Nhặt +50%</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Pickup Range +60%</t>
+          <t>Tầm Nhặt +60%</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Pickup Range +80%</t>
+          <t>Tầm Nhặt +80%</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Movement Speed +10%</t>
+          <t>Tốc Độ Di Chuyển +10%</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Movement Speed +12%</t>
+          <t>Tốc Độ Di Chuyển +12%</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Movement Speed +16%</t>
+          <t>Tốc Độ Di Chuyển +16%</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Pickup Range +50%</t>
+          <t>Tầm Nhặt +50%</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Pickup Range +60%</t>
+          <t>Tầm Nhặt +60%</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Pickup Range +80%</t>
+          <t>Tầm Nhặt +80%</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Recycling</t>
+          <t>Tái Chế</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Quantitative Trading</t>
+          <t>Giao Dịch Định Lượng</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Health Insurance</t>
+          <t>Bảo hiểm sức khỏe</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Windfall</t>
+          <t>Của Trời Cho</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Liquid Market</t>
+          <t>Chợ Lưu Động</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Capital Buffer</t>
+          <t>Bộ đệm Trung tâm</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Asset Restructuring</t>
+          <t>Tái Cấu Trúc Tài Nguyên</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Battlefield Rookie</t>
+          <t>Tân Binh Chiến Trường</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Surplus Value</t>
+          <t>Giá Trị Thặng Dư</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Bulk Trading</t>
+          <t>Giao dịch số lượng lớn</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Project Dividend</t>
+          <t>Dự án Dividend</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Speculative Harvest</t>
+          <t>Thu Hoạch Suy Đoán</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Fake Statements</t>
+          <t>Những Lời Giả Dối</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Short-Term Financing</t>
+          <t>Tài trợ Ngắn Hạn</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>VAM Agreement</t>
+          <t>Thỏa thuận VAM</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Lease Liability</t>
+          <t>Nợ Thuê</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Attack Speed +12%</t>
+          <t>Tốc Độ Tấn Công +12%</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Attack Speed +15%</t>
+          <t>Tốc Độ Tấn Công +15%</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Attack Speed +19%</t>
+          <t>Tốc Độ Tấn Công +19%</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Attack Speed +25%</t>
+          <t>Tốc Độ Tấn Công +25%</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Summon Speed +12%</t>
+          <t>Triệu hồi Tốc Độ +12%</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Summon Speed +15%</t>
+          <t>Triệu hồi Tốc Độ +15%</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Summon Speed +19%</t>
+          <t>Triệu hồi Tốc Độ +19%</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Summon Speed +25%</t>
+          <t>Triệu hồi Tốc Độ +25%</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Chấp Nhận</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Hãy hoàn thành Nhiệm Vụ Exploration "Vào Land Paradox" trước đã.</t>
+          <t>Hãy hoàn thành Nhiệm Vụ Thám Hiểm "Vào Vùng Đất Nghịch Lý" trước đã.</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Tune Break</t>
+          <t>Đột phá Điệu nhạc</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Tune Rupture - Shifting</t>
+          <t>Điều Chỉnh Vết Nứt - Dịch Chuyển.</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Tune Strain - Shifting</t>
+          <t>Tune Strain - Dịch Chuyển</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Tune Rupture - Interfered</t>
+          <t>Điều Chỉnh Vết Nứt - Bị Can Thiệp.</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Tune Strain - Interfered</t>
+          <t>Tune Strain - Giao Thoa</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Afterflame</t>
+          <t>Hậu Lửa</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Sinflame</t>
+          <t>Lửa Tội</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Purging Flame</t>
+          <t>Lửa Thanh Tẩy</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Threshold State</t>
+          <t>Trạng Thái Ngưỡng</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Demon Hypostasis</t>
+          <t>Hóa Thân Ác Quỷ</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Eternal Hypostasis</t>
+          <t>Thực Thể Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Burning Drive</t>
+          <t>Động Lực Cháy Bỏng</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Baseline Mode</t>
+          <t>Chế Độ Cơ Bản</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Wide Field Observation Mode</t>
+          <t>Chế Độ Quan Sát Trường Rộng</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Rest Mass Energy</t>
+          <t>Năng lượng nghỉ khối lượng</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Relative Momentum</t>
+          <t>Động Lượng Tương Đối</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Observation Marker</t>
+          <t>Điểm Quan Sát</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Interfered Marker</t>
+          <t>Điểm Đánh Dấu Bị Nhiễu</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Syntony Field</t>
+          <t>Trường Điều Tần</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>High Syntony Field</t>
+          <t>Trường Cộng Hưởng Cao</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Crown of Wills</t>
+          <t>Vương Miện Ý Chí</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Prowess</t>
+          <t>Kỹ năng</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Ascendancy</t>
+          <t>Thăng Hoa Cấp</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Majesty</t>
+          <t>Uy Nghiêm</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Ruler's Realm</t>
+          <t>Lãnh Địa Của Chúa Tể</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Sworn Allegiance</t>
+          <t>Lời Thề Trung Thành</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Lunar Cycle</t>
+          <t>Chu kỳ Mặt Trăng</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Phúc Lành Light Mờ Ảo</t>
+          <t>Phúc Lành Ánh Sáng Mờ Ảo</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Sentience</t>
+          <t>Ý Thức</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Swordster's Soliloquy</t>
+          <t>Độc Thoại Kiếm Khách</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Inksplash of Mind</t>
+          <t>Mực loang Tâm Trí</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Bamboo's Shade</t>
+          <t>Bóng Tre</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Unseen Snare</t>
+          <t>Bẫy vô hình</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Thread of Bane</t>
+          <t>Sợi Dây Tử Thần</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Nhẫn Chainsaw</t>
+          <t>Nhẫn Cưa Xích</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Lifethread - Jetstream</t>
+          <t>Sợi Sinh Mệnh - Dòng Chảy</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Woven Myriad - Convergence</t>
+          <t>Vô Tận Dệt Nên - Hội Tụ</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Electro Rage</t>
+          <t>Điên Loạn Điện</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Negative Status DMG</t>
+          <t>DMG Trạng thái Tiêu cực</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Optical Sampling Stage</t>
+          <t>Giai Đoạn Lấy Mẫu Quang Học</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Kaleidoscopic Parade</t>
+          <t>Diễu Hành Đa Sắc</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Photochromic Flux</t>
+          <t>Dòng Chảy Quang Sắc</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Spray Paint</t>
+          <t>Phun Sơn</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Overflow</t>
+          <t>Tràn Đầy</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Lumiflow</t>
+          <t>Dòng Lưu Quang</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>True Color</t>
+          <t>Bản Chất Thật</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Volatile Ghi chú</t>
+          <t>Ghi Chú Bất Định</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Resolving Chord</t>
+          <t>Đang kích hoạt Hợp Âm</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Aftersound</t>
+          <t>Dư Âm</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Reincarnate</t>
+          <t>Hóa Thân</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Combo - Rice Dango Missile</t>
+          <t>Hồi Chiêu - Tên Lửa Bánh Dango</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Combo - Rice Dango Missile: Enhanced</t>
+          <t>Hồi Chiêu - Tên Lửa Bánh Dango: Cường Hóa</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Burst - Blazing Pillar</t>
+          <t>Kích Hoạt - Trụ Lửa Bừng Cháy</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Burst - Scorching Impact</t>
+          <t>Kích Hoạt - Cú Đánh Thiêu Đốt</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Boost - Namipon Aid</t>
+          <t>Tăng cường - Hỗ trợ Namipon</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Boost - Sprint</t>
+          <t>Tăng cường - Bứt tốc</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Combo - Hỗ Trợ Missile: Enhanced</t>
+          <t>Hồi Chiêu - Tên Lửa Hỗ Trợ: Cường Hóa</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Combo - Hỗ Trợ Missile</t>
+          <t>Hồi Chiêu - Tên Lửa Hỗ Trợ</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Status - Waveworn Bane</t>
+          <t>Trạng thái - Tai Họa Bị Sóng Bào Mòn</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Boost - Dessert Prep</t>
+          <t>Tăng lực - Chuẩn bị món tráng miệng</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Combo - Dessert Strike</t>
+          <t>Combo - Đòn Đánh Tráng Miệng</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Combo - Dessert Strike: Enhanced</t>
+          <t>Hồi Chiêu - Đòn Tráng Miệng: Cường Hóa</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Boost - Satisfaction</t>
+          <t>Tăng cường - Thỏa mãn</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Burst - Coffee Impact</t>
+          <t>Kích Hoạt - Cú Đánh Cà Phê</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Boost - Coffee's Shelter</t>
+          <t>Tăng lực - Quán Cà Phê Shelter</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Critical State</t>
+          <t>Trạng Thái Bạo Kích</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Burst - Shock Impact</t>
+          <t>Kích Hoạt - Cú Đánh Sốc Điện</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Daylight Pebble</t>
+          <t>Viên Sỏi Ánh Ngày</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Chọn Terminal</t>
+          <t>Chọn Thiết bị đầu cuối</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Switch Terminal</t>
+          <t>Chuyển Thiết bị Đầu Cuối</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Có thể nhận qua</t>
+          <t>Có thể nhận thông qua</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Traces của Thủy Triều I</t>
+          <t>Dấu vết của Thủy Triều I</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Traces của Thủy Triều II</t>
+          <t>Dấu vết của Thủy Triều II</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Traces của Thủy Triều III</t>
+          <t>Dấu vết của Thủy Triều III</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Traces của Thủy Triều IV</t>
+          <t>Dấu vết của Thủy Triều IV</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Traces of Tides V</t>
+          <t>Dấu Vết Thủy Triều V</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Traces of Tides VI</t>
+          <t>Dấu Vết Thủy Triều VI</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Traces of Tides VII</t>
+          <t>Dấu Vết Thủy Triều VII</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Traces of Tides: VIII</t>
+          <t>Dấu Vết Thủy Triều: VIII</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Traces of Tides: IX</t>
+          <t>Dấu Vết Thủy Triều: IX</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Idle Animation: I</t>
+          <t>Động tác chờ: I</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
